--- a/outputs/2_1_tasas_mujeres.xlsx
+++ b/outputs/2_1_tasas_mujeres.xlsx
@@ -17,22 +17,22 @@
     <t xml:space="preserve">Tasas (%) y poblaciones</t>
   </si>
   <si>
+    <t xml:space="preserve">Enero - marzo 2023</t>
+  </si>
+  <si>
     <t xml:space="preserve">Abril - junio 2023</t>
   </si>
   <si>
-    <t xml:space="preserve">Enero - marzo 2023</t>
-  </si>
-  <si>
     <t xml:space="preserve">Julio - septiembre 2023</t>
   </si>
   <si>
     <t xml:space="preserve">Octubre - diciembre 2023</t>
   </si>
   <si>
+    <t xml:space="preserve">Enero - marzo 2024</t>
+  </si>
+  <si>
     <t xml:space="preserve">Abril - junio 2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enero - marzo 2024</t>
   </si>
   <si>
     <t xml:space="preserve">Julio - septiembre 2024</t>
@@ -425,10 +425,10 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
+        <v>52.13</v>
+      </c>
+      <c r="C2" t="n">
         <v>52.75</v>
-      </c>
-      <c r="C2" t="n">
-        <v>52.13</v>
       </c>
       <c r="D2" t="n">
         <v>53.07</v>
@@ -437,10 +437,10 @@
         <v>52.44</v>
       </c>
       <c r="F2" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="G2" t="n">
         <v>52.27</v>
-      </c>
-      <c r="G2" t="n">
-        <v>52.02</v>
       </c>
       <c r="H2" t="n">
         <v>52.69</v>
@@ -454,10 +454,10 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
+        <v>44.26</v>
+      </c>
+      <c r="C3" t="n">
         <v>45.93</v>
-      </c>
-      <c r="C3" t="n">
-        <v>44.26</v>
       </c>
       <c r="D3" t="n">
         <v>46.88</v>
@@ -466,10 +466,10 @@
         <v>46.35</v>
       </c>
       <c r="F3" t="n">
+        <v>44.23</v>
+      </c>
+      <c r="G3" t="n">
         <v>45.64</v>
-      </c>
-      <c r="G3" t="n">
-        <v>44.23</v>
       </c>
       <c r="H3" t="n">
         <v>46.3</v>
@@ -483,10 +483,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="C4" t="n">
         <v>12.92</v>
-      </c>
-      <c r="C4" t="n">
-        <v>15.09</v>
       </c>
       <c r="D4" t="n">
         <v>11.65</v>
@@ -495,10 +495,10 @@
         <v>11.62</v>
       </c>
       <c r="F4" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="G4" t="n">
         <v>12.68</v>
-      </c>
-      <c r="G4" t="n">
-        <v>14.98</v>
       </c>
       <c r="H4" t="n">
         <v>12.12</v>
@@ -512,10 +512,10 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
+        <v>26080284</v>
+      </c>
+      <c r="C5" t="n">
         <v>26152845</v>
-      </c>
-      <c r="C5" t="n">
-        <v>26080284</v>
       </c>
       <c r="D5" t="n">
         <v>26223382</v>
@@ -524,10 +524,10 @@
         <v>26295834</v>
       </c>
       <c r="F5" t="n">
+        <v>26366929</v>
+      </c>
+      <c r="G5" t="n">
         <v>26437712</v>
-      </c>
-      <c r="G5" t="n">
-        <v>26366929</v>
       </c>
       <c r="H5" t="n">
         <v>26506805</v>
@@ -541,10 +541,10 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
+        <v>20454972</v>
+      </c>
+      <c r="C6" t="n">
         <v>20529442</v>
-      </c>
-      <c r="C6" t="n">
-        <v>20454972</v>
       </c>
       <c r="D6" t="n">
         <v>20603334</v>
@@ -553,10 +553,10 @@
         <v>20680445</v>
       </c>
       <c r="F6" t="n">
+        <v>20756972</v>
+      </c>
+      <c r="G6" t="n">
         <v>20833277</v>
-      </c>
-      <c r="G6" t="n">
-        <v>20756972</v>
       </c>
       <c r="H6" t="n">
         <v>20907273</v>
@@ -570,10 +570,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
+        <v>10662324</v>
+      </c>
+      <c r="C7" t="n">
         <v>10829473</v>
-      </c>
-      <c r="C7" t="n">
-        <v>10662324</v>
       </c>
       <c r="D7" t="n">
         <v>10933226</v>
@@ -582,10 +582,10 @@
         <v>10845021</v>
       </c>
       <c r="F7" t="n">
+        <v>10797737</v>
+      </c>
+      <c r="G7" t="n">
         <v>10890556</v>
-      </c>
-      <c r="G7" t="n">
-        <v>10797737</v>
       </c>
       <c r="H7" t="n">
         <v>11016301</v>
@@ -599,10 +599,10 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
+        <v>9053858</v>
+      </c>
+      <c r="C8" t="n">
         <v>9429973</v>
-      </c>
-      <c r="C8" t="n">
-        <v>9053858</v>
       </c>
       <c r="D8" t="n">
         <v>9659727</v>
@@ -611,10 +611,10 @@
         <v>9585297</v>
       </c>
       <c r="F8" t="n">
+        <v>9180448</v>
+      </c>
+      <c r="G8" t="n">
         <v>9509175</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9180448</v>
       </c>
       <c r="H8" t="n">
         <v>9680991</v>
@@ -628,10 +628,10 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
+        <v>1608466</v>
+      </c>
+      <c r="C9" t="n">
         <v>1399500</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1608466</v>
       </c>
       <c r="D9" t="n">
         <v>1273499</v>
@@ -640,10 +640,10 @@
         <v>1259724</v>
       </c>
       <c r="F9" t="n">
+        <v>1617289</v>
+      </c>
+      <c r="G9" t="n">
         <v>1381381</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1617289</v>
       </c>
       <c r="H9" t="n">
         <v>1335310</v>
